--- a/.ganttChartArchive/線表_TeamColliders_20250514.xlsx
+++ b/.ganttChartArchive/線表_TeamColliders_20250514.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haru/Documents/GitHub/TeamColliders/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitReps\TeamColliders\.ganttChartArchive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91E58F62-239F-B745-B0F4-D29A09471C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1535603F-AC2C-4732-A0E1-54DDE3A7A3E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="記入例（第４週）" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="94">
   <si>
     <t>チーム名</t>
   </si>
@@ -630,16 +630,20 @@
   <si>
     <t>全員</t>
   </si>
+  <si>
+    <t>V2</t>
+    <phoneticPr fontId="37"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="yy&quot;年 &quot;m&quot;月 &quot;d&quot;日&quot;"/>
-    <numFmt numFmtId="165" formatCode="mm&quot;/&quot;dd"/>
-    <numFmt numFmtId="166" formatCode="d"/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="176" formatCode="yy&quot;年 &quot;m&quot;月 &quot;d&quot;日&quot;"/>
+    <numFmt numFmtId="177" formatCode="mm&quot;/&quot;dd"/>
+    <numFmt numFmtId="178" formatCode="d"/>
+    <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="81">
     <font>
@@ -921,7 +925,7 @@
     <font>
       <sz val="9"/>
       <color rgb="FF7030A0"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -929,7 +933,7 @@
     <font>
       <sz val="9"/>
       <color theme="9" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -937,7 +941,7 @@
     <font>
       <sz val="12"/>
       <color theme="9" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -945,14 +949,14 @@
     <font>
       <sz val="9"/>
       <color rgb="FF0B5394"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -960,7 +964,7 @@
     <font>
       <sz val="9"/>
       <color rgb="FFA64D79"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -968,7 +972,7 @@
     <font>
       <sz val="9"/>
       <color rgb="FF45818E"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -976,7 +980,7 @@
     <font>
       <sz val="9"/>
       <color rgb="FFB85B22"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -984,7 +988,7 @@
     <font>
       <sz val="9"/>
       <color rgb="FF38761D"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -992,7 +996,7 @@
     <font>
       <sz val="9"/>
       <color rgb="FF351C75"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1001,7 +1005,7 @@
       <b/>
       <sz val="14"/>
       <color rgb="FFBF9000"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1010,7 +1014,7 @@
       <b/>
       <sz val="14"/>
       <color rgb="FF0B5394"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1018,7 +1022,7 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1027,7 +1031,7 @@
       <b/>
       <sz val="14"/>
       <color rgb="FFA64D79"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1036,7 +1040,7 @@
       <b/>
       <sz val="14"/>
       <color rgb="FF45818E"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1045,7 +1049,7 @@
       <b/>
       <sz val="14"/>
       <color rgb="FFB85B22"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1054,7 +1058,7 @@
       <b/>
       <sz val="14"/>
       <color rgb="FF38761D"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1063,7 +1067,7 @@
       <b/>
       <sz val="14"/>
       <color rgb="FF351C75"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1071,7 +1075,7 @@
     <font>
       <sz val="12"/>
       <color rgb="FF7030A0"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1079,7 +1083,7 @@
     <font>
       <sz val="9"/>
       <color theme="7" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1087,7 +1091,7 @@
     <font>
       <sz val="12"/>
       <color theme="7" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1830,10 +1834,10 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1868,7 +1872,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="23" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1886,7 +1890,7 @@
     <xf numFmtId="9" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2202,16 +2206,16 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="50" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="50" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="50" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="50" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="50" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="50" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="50" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="50" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="65" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2275,7 +2279,7 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="76" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="76" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2317,7 +2321,7 @@
     <xf numFmtId="49" fontId="55" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="76" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="76" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2438,7 +2442,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="55" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="22" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="32" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2469,7 +2473,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3860,12 +3864,8 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -4166,17 +4166,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:BT38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13.5" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="13.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.83203125" customWidth="1"/>
-    <col min="2" max="2" width="7.1640625" customWidth="1"/>
-    <col min="3" max="3" width="1.1640625" customWidth="1"/>
-    <col min="4" max="5" width="8.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="9.1640625" customWidth="1"/>
+    <col min="1" max="1" width="3.875" customWidth="1"/>
+    <col min="2" max="2" width="7.125" customWidth="1"/>
+    <col min="3" max="3" width="1.125" customWidth="1"/>
+    <col min="4" max="5" width="8.875" customWidth="1"/>
+    <col min="6" max="6" width="10.875" customWidth="1"/>
+    <col min="7" max="7" width="9.125" customWidth="1"/>
     <col min="8" max="8" width="11.5" customWidth="1"/>
-    <col min="9" max="9" width="6.1640625" customWidth="1"/>
-    <col min="10" max="72" width="2.83203125" customWidth="1"/>
+    <col min="9" max="9" width="6.125" customWidth="1"/>
+    <col min="10" max="72" width="2.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:72" ht="21" customHeight="1">
@@ -4645,7 +4645,7 @@
       <c r="BS6" s="26"/>
       <c r="BT6" s="26"/>
     </row>
-    <row r="7" spans="1:72" ht="23.5" customHeight="1">
+    <row r="7" spans="1:72" ht="23.45" customHeight="1">
       <c r="A7" s="26"/>
       <c r="B7" s="29"/>
       <c r="C7" s="29"/>
@@ -7421,17 +7421,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:BT37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13.5" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="13.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.83203125" customWidth="1"/>
-    <col min="2" max="2" width="7.1640625" customWidth="1"/>
-    <col min="3" max="3" width="1.1640625" customWidth="1"/>
-    <col min="4" max="5" width="8.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="9.1640625" customWidth="1"/>
+    <col min="1" max="1" width="3.875" customWidth="1"/>
+    <col min="2" max="2" width="7.125" customWidth="1"/>
+    <col min="3" max="3" width="1.125" customWidth="1"/>
+    <col min="4" max="5" width="8.875" customWidth="1"/>
+    <col min="6" max="6" width="10.875" customWidth="1"/>
+    <col min="7" max="7" width="9.125" customWidth="1"/>
     <col min="8" max="8" width="11.5" customWidth="1"/>
-    <col min="9" max="9" width="6.1640625" customWidth="1"/>
-    <col min="10" max="72" width="2.83203125" customWidth="1"/>
+    <col min="9" max="9" width="6.125" customWidth="1"/>
+    <col min="10" max="72" width="2.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:72" ht="21" customHeight="1">
@@ -7900,7 +7900,7 @@
       <c r="BS6" s="26"/>
       <c r="BT6" s="26"/>
     </row>
-    <row r="7" spans="1:72" ht="23.5" customHeight="1">
+    <row r="7" spans="1:72" ht="23.45" customHeight="1">
       <c r="A7" s="26"/>
       <c r="B7" s="29"/>
       <c r="C7" s="29"/>
@@ -10620,18 +10620,18 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:XFD38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13.5" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="13.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.83203125" customWidth="1"/>
-    <col min="2" max="2" width="7.1640625" customWidth="1"/>
-    <col min="3" max="3" width="1.1640625" customWidth="1"/>
-    <col min="4" max="4" width="9.83203125" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="9.1640625" customWidth="1"/>
+    <col min="1" max="1" width="3.875" customWidth="1"/>
+    <col min="2" max="2" width="7.125" customWidth="1"/>
+    <col min="3" max="3" width="1.125" customWidth="1"/>
+    <col min="4" max="4" width="9.875" customWidth="1"/>
+    <col min="5" max="5" width="8.875" customWidth="1"/>
+    <col min="6" max="6" width="10.875" customWidth="1"/>
+    <col min="7" max="7" width="9.125" customWidth="1"/>
     <col min="8" max="8" width="11.5" customWidth="1"/>
-    <col min="9" max="9" width="6.1640625" customWidth="1"/>
-    <col min="10" max="72" width="2.83203125" customWidth="1"/>
+    <col min="9" max="9" width="6.125" customWidth="1"/>
+    <col min="10" max="72" width="2.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:72" ht="21" customHeight="1">
@@ -11100,7 +11100,7 @@
       <c r="BS6" s="26"/>
       <c r="BT6" s="26"/>
     </row>
-    <row r="7" spans="1:72" ht="23.5" customHeight="1">
+    <row r="7" spans="1:72" ht="23.45" customHeight="1">
       <c r="A7" s="26"/>
       <c r="B7" s="29"/>
       <c r="C7" s="29"/>
@@ -13885,18 +13885,18 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:XFD38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13.5" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="13.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.83203125" customWidth="1"/>
-    <col min="2" max="2" width="7.1640625" customWidth="1"/>
-    <col min="3" max="3" width="1.1640625" customWidth="1"/>
-    <col min="4" max="4" width="9.83203125" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="9.1640625" customWidth="1"/>
+    <col min="1" max="1" width="3.875" customWidth="1"/>
+    <col min="2" max="2" width="7.125" customWidth="1"/>
+    <col min="3" max="3" width="1.125" customWidth="1"/>
+    <col min="4" max="4" width="9.875" customWidth="1"/>
+    <col min="5" max="5" width="8.875" customWidth="1"/>
+    <col min="6" max="6" width="10.875" customWidth="1"/>
+    <col min="7" max="7" width="9.125" customWidth="1"/>
     <col min="8" max="8" width="11.5" customWidth="1"/>
-    <col min="9" max="9" width="6.1640625" customWidth="1"/>
-    <col min="10" max="72" width="2.83203125" customWidth="1"/>
+    <col min="9" max="9" width="6.125" customWidth="1"/>
+    <col min="10" max="72" width="2.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:72" ht="21" customHeight="1">
@@ -14144,7 +14144,7 @@
       <c r="L4" s="150"/>
       <c r="M4" s="150"/>
       <c r="N4" s="151">
-        <v>45784</v>
+        <v>45791</v>
       </c>
       <c r="O4" s="148"/>
       <c r="P4" s="148"/>
@@ -14226,7 +14226,7 @@
       <c r="L5" s="150"/>
       <c r="M5" s="150"/>
       <c r="N5" s="151" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="O5" s="148"/>
       <c r="P5" s="148"/>
@@ -14365,7 +14365,7 @@
       <c r="BS6" s="26"/>
       <c r="BT6" s="26"/>
     </row>
-    <row r="7" spans="1:72" ht="23.5" customHeight="1">
+    <row r="7" spans="1:72" ht="23.45" customHeight="1">
       <c r="A7" s="26"/>
       <c r="B7" s="29"/>
       <c r="C7" s="29"/>
@@ -17118,11 +17118,6 @@
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="G14:H14"/>
-    <mergeCell ref="AH8:AI8"/>
-    <mergeCell ref="AO8:AP8"/>
-    <mergeCell ref="AV8:AW8"/>
-    <mergeCell ref="BC8:BD8"/>
-    <mergeCell ref="BJ8:BK8"/>
     <mergeCell ref="BQ8:BR8"/>
     <mergeCell ref="D5:G5"/>
     <mergeCell ref="J5:M5"/>
@@ -17130,6 +17125,11 @@
     <mergeCell ref="M8:N8"/>
     <mergeCell ref="T8:U8"/>
     <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="AH8:AI8"/>
+    <mergeCell ref="AO8:AP8"/>
+    <mergeCell ref="AV8:AW8"/>
+    <mergeCell ref="BC8:BD8"/>
+    <mergeCell ref="BJ8:BK8"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="J2:O2"/>
     <mergeCell ref="P2:AK2"/>
@@ -17137,6 +17137,7 @@
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="N4:Q4"/>
   </mergeCells>
+  <phoneticPr fontId="37"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
